--- a/AAA/AAA_AAA/006_AKU1/条件输入数据表.xlsx
+++ b/AAA/AAA_AAA/006_AKU1/条件输入数据表.xlsx
@@ -1779,12 +1779,12 @@
       </c>
       <c r="D2" s="21" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -2530,9 +2530,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2592,7 +2592,7 @@
       <c r="C2" s="21" t="inlineStr"/>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>/</t>
         </is>
       </c>
     </row>
